--- a/output/pdf_financials_xlsx/IMR.xlsx
+++ b/output/pdf_financials_xlsx/IMR.xlsx
@@ -1279,10 +1279,10 @@
         <v>-1.761779</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>-1.319571</v>
@@ -1579,10 +1579,10 @@
         <v>-1.761779</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-1.319571</v>
@@ -1753,10 +1753,10 @@
         <v>-1.761779</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>-1.319571</v>
@@ -2021,10 +2021,10 @@
         <v>-1.761779</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.319571</v>
@@ -2137,10 +2137,10 @@
         <v>-1.761779</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.319571</v>
@@ -2287,10 +2287,10 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>-0</v>
@@ -5929,52 +5929,52 @@
         <v>1.687918</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.894432</v>
+        <v>3.272174</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.403584</v>
+        <v>4.053198</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.21702</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.413194</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.714303</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.714303</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.950013</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.055142</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.220597</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.396065</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.432598</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.875598</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.638719</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>4.634146</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>4.675092</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.836146</v>
       </c>
     </row>
     <row r="93">
@@ -6515,13 +6515,13 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>0.023092</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>0.002236</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.15002</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>-0.026682</v>
@@ -7391,13 +7391,13 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.438245</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.193621</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>0.308268</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>1.422578</v>
@@ -9772,7 +9772,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -10423,7 +10427,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11118,7 +11126,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -11518,7 +11530,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -12118,7 +12134,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -12930,7 +12950,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -14249,7 +14273,11 @@
           <t>Share-based payment reserve (Note 14)</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -15344,7 +15372,11 @@
           <t>Reserves (Note 14)</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -38302,7 +38334,11 @@
           <t>Write-off of exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
           <t>-</t>
@@ -40011,7 +40047,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E318" t="inlineStr">
         <is>
           <t>-</t>
@@ -43669,7 +43709,11 @@
           <t>Prepaid and deposits</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E354" s="5" t="n">
         <v>0.023092</v>
       </c>
@@ -65958,10 +66002,10 @@
         </is>
       </c>
       <c r="G577" s="5" t="n">
-        <v>0.337075</v>
+        <v>-0.337075</v>
       </c>
       <c r="H577" s="5" t="n">
-        <v>1.333984</v>
+        <v>-1.333984</v>
       </c>
       <c r="I577" t="inlineStr">
         <is>
@@ -66160,10 +66204,10 @@
         </is>
       </c>
       <c r="G579" s="5" t="n">
-        <v>0.356075</v>
+        <v>-0.356075</v>
       </c>
       <c r="H579" s="5" t="n">
-        <v>1.343984</v>
+        <v>-1.343984</v>
       </c>
       <c r="I579" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/IMR.xlsx
+++ b/output/pdf_financials_xlsx/IMR.xlsx
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003033</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-5.2e-05</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-1.9e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003452</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2015,16 +2015,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-1.939699</v>
+        <v>-1.936666</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.761779</v>
+        <v>-1.761727</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.337075</v>
+        <v>-0.337056</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.333984</v>
+        <v>-1.330532</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-1.319571</v>
@@ -2131,16 +2131,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-1.939699</v>
+        <v>-1.936666</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.761779</v>
+        <v>-1.761727</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.337075</v>
+        <v>-0.337056</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.333984</v>
+        <v>-1.330532</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-1.319571</v>
@@ -2444,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.019652</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.142827</v>
@@ -2453,40 +2453,40 @@
         <v>0.017245</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>9e-06</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.005009</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.197986</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.362956</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.140997</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.593705</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.000858</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.882471</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>1.984495</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.893539</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.012369</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.157878</v>
       </c>
     </row>
     <row r="35">
@@ -2560,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.223991</v>
+        <v>0.243643</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.142827</v>
@@ -2569,40 +2569,40 @@
         <v>0.017245</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.006266</v>
+        <v>0.006275</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.005009</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.197986</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.362956</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.140997</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.593705</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.000858</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.882471</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>1.984495</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.893539</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.012369</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.157878</v>
       </c>
     </row>
     <row r="37">
@@ -3256,7 +3256,7 @@
         <v>0.008300999999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.177973</v>
+        <v>0.158321</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.026682</v>
@@ -3268,37 +3268,37 @@
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.005009</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.199299</v>
+        <v>0.001313</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.386883</v>
+        <v>0.023927</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.154758</v>
+        <v>0.013761</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.678365</v>
+        <v>0.08466</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.016003</v>
+        <v>0.015145</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.98503</v>
+        <v>0.102559</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>2.051686</v>
+        <v>0.067191</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.037299</v>
+        <v>0.14376</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.076818</v>
+        <v>0.06444900000000001</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.231858</v>
+        <v>0.07398</v>
       </c>
     </row>
     <row r="49">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -54953,7 +54953,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -63275,7 +63275,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -65784,7 +65784,7 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
@@ -68988,7 +68988,7 @@
       </c>
       <c r="D607" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E607" s="5" t="n">

--- a/output/pdf_financials_xlsx/IMR.xlsx
+++ b/output/pdf_financials_xlsx/IMR.xlsx
@@ -7055,7 +7055,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.070553</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -36027,7 +36027,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E278" t="inlineStr">
         <is>
           <t>-</t>
@@ -36328,7 +36332,11 @@
           <t>Proceeds (net) from disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E281" t="inlineStr">
         <is>
           <t>-</t>
